--- a/CastleHero_Table/Character_Table.xlsx
+++ b/CastleHero_Table/Character_Table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\castle-hero\CastleHero_Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78475232-DCD9-42F2-A033-D24DC7501903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A228D195-E7C6-40D1-82B1-5909BCFDEA18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39280" yWindow="780" windowWidth="30660" windowHeight="19010" xr2:uid="{3CA33FF5-4092-4742-9739-7C695FCFC701}"/>
+    <workbookView xWindow="6280" yWindow="1250" windowWidth="30670" windowHeight="19010" xr2:uid="{3CA33FF5-4092-4742-9739-7C695FCFC701}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Character_ID</t>
   </si>
@@ -95,118 +95,7 @@
     <t>Character_Range_Move</t>
   </si>
   <si>
-    <t>캐릭터의 고유 ID</t>
-  </si>
-  <si>
-    <t>캐릭터 아이콘 파일명</t>
-  </si>
-  <si>
-    <t>캐릭터의 이름</t>
-  </si>
-  <si>
-    <t>캐릭터의 태생 등급 입력</t>
-  </si>
-  <si>
-    <t>팀 구분</t>
-  </si>
-  <si>
-    <t>스킬 ID</t>
-  </si>
-  <si>
-    <t>캐릭터 직업</t>
-  </si>
-  <si>
-    <t>공중/지상 공격 타입</t>
-  </si>
-  <si>
-    <t>공중/지상 방어 타입</t>
-  </si>
-  <si>
-    <t>공격 우선순위</t>
-  </si>
-  <si>
-    <t>부활 시간</t>
-  </si>
-  <si>
-    <t>스테이터스 체력</t>
-  </si>
-  <si>
-    <t>스테이터스 공격력</t>
-  </si>
-  <si>
-    <t>스테이터스 치명타율</t>
-  </si>
-  <si>
-    <t>스테이터스 치명타 피해</t>
-  </si>
-  <si>
-    <t>공격 속도</t>
-  </si>
-  <si>
-    <t>이동 속도</t>
-  </si>
-  <si>
-    <t>공격 범위</t>
-  </si>
-  <si>
-    <t>이동 범위</t>
-  </si>
-  <si>
     <t>암살자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1 탱커	
-2 근거리	
-3 원거리	
-4 마법	
-5 힐러	</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0 전설
-1 에픽
-2 레어
-3 일반</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1 망자
-2 분노
-3 몽마
-4 악마
-5 미치광이
-6 순찰대
-7 몬스터
-8 야수
-9 거인
-10 깃털</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>캐릭터 10000
-몬스터 20000
-보스 30000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0 전체 공격
-1 지상 공격
-2 공중 공격</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1 지상 방어
-2 공중 방어</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0 공성
-1 전투
-2 공중 대상
-3 지상 대상
-4 원거리 대상
-5 근거리 대상</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -299,18 +188,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -652,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71CD3EA9-81B6-49C4-B82B-EED3EC8E1451}">
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.9140625" style="1" bestFit="1" customWidth="1"/>
@@ -676,165 +559,201 @@
     <col min="20" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="3" customFormat="1" ht="165" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>45</v>
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1">
+        <v>10021</v>
+      </c>
+      <c r="B2" s="1">
+        <v>10021</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="1" t="s">
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>6</v>
+      </c>
+      <c r="F2" s="1">
+        <v>10021</v>
+      </c>
+      <c r="G2" s="1">
+        <v>2</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1</v>
+      </c>
+      <c r="K2" s="1">
         <v>30</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>37</v>
+      <c r="L2" s="1">
+        <v>300</v>
+      </c>
+      <c r="M2" s="1">
+        <v>100</v>
+      </c>
+      <c r="N2" s="1">
+        <v>30</v>
+      </c>
+      <c r="O2" s="1">
+        <v>50</v>
+      </c>
+      <c r="P2" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>3</v>
+      </c>
+      <c r="R2" s="1">
+        <v>1</v>
+      </c>
+      <c r="S2" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="A3" s="1">
+        <v>20001</v>
+      </c>
+      <c r="B3" s="1">
+        <v>20001</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="1">
         <v>3</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="5" t="s">
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1">
+        <v>20001</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0</v>
+      </c>
+      <c r="L3" s="1">
+        <v>200</v>
+      </c>
+      <c r="M3" s="1">
         <v>10</v>
       </c>
-      <c r="L3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>18</v>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>1</v>
+      </c>
+      <c r="R3" s="1">
+        <v>2</v>
+      </c>
+      <c r="S3" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
-        <v>10021</v>
+        <v>20002</v>
       </c>
       <c r="B4" s="1">
-        <v>10021</v>
+        <v>20002</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F4" s="1">
-        <v>10021</v>
+        <v>20002</v>
       </c>
       <c r="G4" s="1">
         <v>2</v>
@@ -849,42 +768,42 @@
         <v>1</v>
       </c>
       <c r="K4" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L4" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M4" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="N4" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O4" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S4" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
-        <v>20001</v>
+        <v>20003</v>
       </c>
       <c r="B5" s="1">
-        <v>20001</v>
+        <v>20003</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -893,7 +812,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="1">
-        <v>20001</v>
+        <v>20003</v>
       </c>
       <c r="G5" s="1">
         <v>2</v>
@@ -911,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="1">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M5" s="1">
         <v>10</v>
@@ -923,36 +842,36 @@
         <v>0</v>
       </c>
       <c r="P5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q5" s="1">
         <v>1</v>
       </c>
       <c r="R5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
-        <v>20002</v>
+        <v>30003</v>
       </c>
       <c r="B6" s="1">
-        <v>20002</v>
+        <v>30003</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
         <v>3</v>
       </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
       <c r="F6" s="1">
-        <v>20002</v>
+        <v>30003</v>
       </c>
       <c r="G6" s="1">
         <v>2</v>
@@ -970,145 +889,27 @@
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="M6" s="1">
+        <v>30</v>
+      </c>
+      <c r="N6" s="1">
         <v>10</v>
       </c>
-      <c r="N6" s="1">
-        <v>0</v>
-      </c>
       <c r="O6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="1">
         <v>1</v>
       </c>
       <c r="R6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S6" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A7" s="1">
-        <v>20003</v>
-      </c>
-      <c r="B7" s="1">
-        <v>20003</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="1">
-        <v>3</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1">
-        <v>20003</v>
-      </c>
-      <c r="G7" s="1">
-        <v>2</v>
-      </c>
-      <c r="H7" s="1">
-        <v>1</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1</v>
-      </c>
-      <c r="J7" s="1">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-      <c r="L7" s="1">
-        <v>300</v>
-      </c>
-      <c r="M7" s="1">
-        <v>10</v>
-      </c>
-      <c r="N7" s="1">
-        <v>0</v>
-      </c>
-      <c r="O7" s="1">
-        <v>0</v>
-      </c>
-      <c r="P7" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>1</v>
-      </c>
-      <c r="R7" s="1">
-        <v>1</v>
-      </c>
-      <c r="S7" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A8" s="1">
-        <v>30003</v>
-      </c>
-      <c r="B8" s="1">
-        <v>30003</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1">
-        <v>3</v>
-      </c>
-      <c r="F8" s="1">
-        <v>30003</v>
-      </c>
-      <c r="G8" s="1">
-        <v>2</v>
-      </c>
-      <c r="H8" s="1">
-        <v>1</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1</v>
-      </c>
-      <c r="J8" s="1">
-        <v>1</v>
-      </c>
-      <c r="K8" s="1">
-        <v>0</v>
-      </c>
-      <c r="L8" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M8" s="1">
-        <v>30</v>
-      </c>
-      <c r="N8" s="1">
-        <v>10</v>
-      </c>
-      <c r="O8" s="1">
-        <v>100</v>
-      </c>
-      <c r="P8" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>1</v>
-      </c>
-      <c r="R8" s="1">
-        <v>3</v>
-      </c>
-      <c r="S8" s="1">
         <v>3</v>
       </c>
     </row>

--- a/CastleHero_Table/Character_Table.xlsx
+++ b/CastleHero_Table/Character_Table.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\castle-hero\CastleHero_Table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\CH_Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A228D195-E7C6-40D1-82B1-5909BCFDEA18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0995BB51-97AD-480D-9A3D-66239C78687A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6280" yWindow="1250" windowWidth="30670" windowHeight="19010" xr2:uid="{3CA33FF5-4092-4742-9739-7C695FCFC701}"/>
   </bookViews>

--- a/CastleHero_Table/Character_Table.xlsx
+++ b/CastleHero_Table/Character_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\CH_Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0995BB51-97AD-480D-9A3D-66239C78687A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BA8ECF-1545-41E4-9B6E-35AAE50BA80D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6280" yWindow="1250" windowWidth="30670" windowHeight="19010" xr2:uid="{3CA33FF5-4092-4742-9739-7C695FCFC701}"/>
+    <workbookView xWindow="2660" yWindow="1220" windowWidth="30700" windowHeight="19010" xr2:uid="{3CA33FF5-4092-4742-9739-7C695FCFC701}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>Character_ID</t>
   </si>
@@ -112,6 +112,38 @@
   </si>
   <si>
     <t>기사단장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character_Prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character_Skin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character_10021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster_20001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster_30003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -188,7 +220,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -199,6 +231,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -535,90 +573,97 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71CD3EA9-81B6-49C4-B82B-EED3EC8E1451}">
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.9140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.08203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.4140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.08203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="15.08203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.9140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="8.6640625" style="1"/>
+    <col min="3" max="4" width="16.08203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.4140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="15.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.9140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>10021</v>
       </c>
@@ -626,58 +671,61 @@
         <v>10021</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="1">
-        <v>0</v>
-      </c>
-      <c r="E2" s="1">
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
         <v>6</v>
       </c>
-      <c r="F2" s="1">
+      <c r="H2" s="1">
         <v>10021</v>
       </c>
-      <c r="G2" s="1">
-        <v>2</v>
-      </c>
-      <c r="H2" s="1">
-        <v>1</v>
-      </c>
       <c r="I2" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" s="1">
         <v>1</v>
       </c>
       <c r="K2" s="1">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1">
+        <v>1</v>
+      </c>
+      <c r="M2" s="1">
         <v>30</v>
       </c>
-      <c r="L2" s="1">
+      <c r="N2" s="1">
         <v>300</v>
       </c>
-      <c r="M2" s="1">
+      <c r="O2" s="1">
         <v>100</v>
       </c>
-      <c r="N2" s="1">
+      <c r="P2" s="1">
         <v>30</v>
       </c>
-      <c r="O2" s="1">
+      <c r="Q2" s="1">
         <v>50</v>
       </c>
-      <c r="P2" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="1">
+      <c r="R2" s="1">
+        <v>1</v>
+      </c>
+      <c r="S2" s="1">
         <v>3</v>
       </c>
-      <c r="R2" s="1">
-        <v>1</v>
-      </c>
-      <c r="S2" s="1">
+      <c r="T2" s="1">
+        <v>1</v>
+      </c>
+      <c r="U2" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>20001</v>
       </c>
@@ -685,58 +733,64 @@
         <v>20001</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="1">
+      <c r="F3" s="1">
         <v>3</v>
       </c>
-      <c r="E3" s="1">
-        <v>1</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="G3" s="1">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1">
         <v>20001</v>
       </c>
-      <c r="G3" s="1">
-        <v>2</v>
-      </c>
-      <c r="H3" s="1">
-        <v>1</v>
-      </c>
       <c r="I3" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" s="1">
         <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="1">
+        <v>1</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1">
         <v>200</v>
       </c>
-      <c r="M3" s="1">
+      <c r="O3" s="1">
         <v>10</v>
       </c>
-      <c r="N3" s="1">
-        <v>0</v>
-      </c>
-      <c r="O3" s="1">
-        <v>0</v>
-      </c>
       <c r="P3" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" s="1">
         <v>2</v>
       </c>
       <c r="S3" s="1">
+        <v>1</v>
+      </c>
+      <c r="T3" s="1">
+        <v>2</v>
+      </c>
+      <c r="U3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>20002</v>
       </c>
@@ -744,58 +798,64 @@
         <v>20002</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="1">
+      <c r="F4" s="1">
         <v>3</v>
       </c>
-      <c r="E4" s="1">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1">
         <v>20002</v>
       </c>
-      <c r="G4" s="1">
-        <v>2</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1</v>
-      </c>
       <c r="I4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" s="1">
         <v>1</v>
       </c>
       <c r="K4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="1">
+        <v>1</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1">
         <v>200</v>
       </c>
-      <c r="M4" s="1">
+      <c r="O4" s="1">
         <v>10</v>
       </c>
-      <c r="N4" s="1">
-        <v>0</v>
-      </c>
-      <c r="O4" s="1">
-        <v>0</v>
-      </c>
       <c r="P4" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" s="1">
         <v>2</v>
       </c>
       <c r="S4" s="1">
+        <v>1</v>
+      </c>
+      <c r="T4" s="1">
+        <v>2</v>
+      </c>
+      <c r="U4" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>20003</v>
       </c>
@@ -803,58 +863,64 @@
         <v>20003</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="1">
+      <c r="F5" s="1">
         <v>3</v>
       </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1">
         <v>20003</v>
       </c>
-      <c r="G5" s="1">
-        <v>2</v>
-      </c>
-      <c r="H5" s="1">
-        <v>1</v>
-      </c>
       <c r="I5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
       </c>
       <c r="K5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="1">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
         <v>300</v>
       </c>
-      <c r="M5" s="1">
+      <c r="O5" s="1">
         <v>10</v>
       </c>
-      <c r="N5" s="1">
-        <v>0</v>
-      </c>
-      <c r="O5" s="1">
-        <v>0</v>
-      </c>
       <c r="P5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1">
         <v>3</v>
       </c>
-      <c r="Q5" s="1">
-        <v>1</v>
-      </c>
-      <c r="R5" s="1">
-        <v>1</v>
-      </c>
       <c r="S5" s="1">
         <v>1</v>
       </c>
+      <c r="T5" s="1">
+        <v>1</v>
+      </c>
+      <c r="U5" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>30003</v>
       </c>
@@ -862,54 +928,58 @@
         <v>30003</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="1">
-        <v>0</v>
-      </c>
-      <c r="E6" s="1">
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
         <v>3</v>
       </c>
-      <c r="F6" s="1">
+      <c r="H6" s="1">
         <v>30003</v>
       </c>
-      <c r="G6" s="1">
-        <v>2</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1</v>
-      </c>
       <c r="I6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" s="1">
         <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
         <v>1000</v>
       </c>
-      <c r="M6" s="1">
+      <c r="O6" s="1">
         <v>30</v>
       </c>
-      <c r="N6" s="1">
+      <c r="P6" s="1">
         <v>10</v>
       </c>
-      <c r="O6" s="1">
+      <c r="Q6" s="1">
         <v>100</v>
       </c>
-      <c r="P6" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>1</v>
-      </c>
       <c r="R6" s="1">
+        <v>1</v>
+      </c>
+      <c r="S6" s="1">
+        <v>1</v>
+      </c>
+      <c r="T6" s="1">
         <v>3</v>
       </c>
-      <c r="S6" s="1">
+      <c r="U6" s="1">
         <v>3</v>
       </c>
     </row>

--- a/CastleHero_Table/Character_Table.xlsx
+++ b/CastleHero_Table/Character_Table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\CH_Table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\작업폴더\01. 캐슬히어로\CH_Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BA8ECF-1545-41E4-9B6E-35AAE50BA80D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F903A3-22E5-4027-924A-7DA5C6E67833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="1220" windowWidth="30700" windowHeight="19010" xr2:uid="{3CA33FF5-4092-4742-9739-7C695FCFC701}"/>
+    <workbookView xWindow="43580" yWindow="1150" windowWidth="30700" windowHeight="19010" xr2:uid="{3CA33FF5-4092-4742-9739-7C695FCFC701}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -573,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71CD3EA9-81B6-49C4-B82B-EED3EC8E1451}">
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.9140625" style="1" bestFit="1" customWidth="1"/>
@@ -701,16 +701,16 @@
         <v>30</v>
       </c>
       <c r="N2" s="1">
-        <v>300</v>
+        <v>3000</v>
       </c>
       <c r="O2" s="1">
         <v>100</v>
       </c>
       <c r="P2" s="1">
-        <v>30</v>
+        <v>0.3</v>
       </c>
       <c r="Q2" s="1">
-        <v>50</v>
+        <v>1.5</v>
       </c>
       <c r="R2" s="1">
         <v>1</v>
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="U2" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
@@ -769,7 +769,7 @@
         <v>200</v>
       </c>
       <c r="O3" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P3" s="1">
         <v>0</v>
@@ -784,10 +784,10 @@
         <v>1</v>
       </c>
       <c r="T3" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U3" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.45">
@@ -834,7 +834,7 @@
         <v>200</v>
       </c>
       <c r="O4" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P4" s="1">
         <v>0</v>
@@ -849,10 +849,10 @@
         <v>1</v>
       </c>
       <c r="T4" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U4" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.45">
@@ -899,7 +899,7 @@
         <v>300</v>
       </c>
       <c r="O5" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P5" s="1">
         <v>0</v>
@@ -962,13 +962,13 @@
         <v>1000</v>
       </c>
       <c r="O6" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="P6" s="1">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="Q6" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="R6" s="1">
         <v>1</v>
@@ -977,10 +977,16 @@
         <v>1</v>
       </c>
       <c r="T6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U6" s="1">
         <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="10:10" x14ac:dyDescent="0.45">
+      <c r="J35" s="1">
+        <f>35*300</f>
+        <v>10500</v>
       </c>
     </row>
   </sheetData>

--- a/CastleHero_Table/Character_Table.xlsx
+++ b/CastleHero_Table/Character_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\작업폴더\01. 캐슬히어로\CH_Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F903A3-22E5-4027-924A-7DA5C6E67833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61539DD9-5858-416A-89C1-3D13BDF4C3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43580" yWindow="1150" windowWidth="30700" windowHeight="19010" xr2:uid="{3CA33FF5-4092-4742-9739-7C695FCFC701}"/>
+    <workbookView xWindow="44670" yWindow="1240" windowWidth="30700" windowHeight="19010" xr2:uid="{3CA33FF5-4092-4742-9739-7C695FCFC701}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>Character_ID</t>
   </si>
@@ -144,6 +144,14 @@
   </si>
   <si>
     <t>03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character_10342</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하피</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -573,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71CD3EA9-81B6-49C4-B82B-EED3EC8E1451}">
-  <dimension ref="A1:U35"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.9140625" style="1" bestFit="1" customWidth="1"/>
@@ -727,84 +735,81 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
-        <v>20001</v>
+        <v>10034</v>
       </c>
       <c r="B3" s="1">
-        <v>20001</v>
+        <v>10034</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>9</v>
+      </c>
+      <c r="H3" s="1">
+        <v>10034</v>
+      </c>
+      <c r="I3" s="1">
         <v>3</v>
       </c>
-      <c r="G3" s="1">
-        <v>1</v>
-      </c>
-      <c r="H3" s="1">
-        <v>20001</v>
-      </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1">
         <v>2</v>
       </c>
-      <c r="J3" s="1">
-        <v>1</v>
-      </c>
-      <c r="K3" s="1">
-        <v>1</v>
-      </c>
       <c r="L3" s="1">
         <v>1</v>
       </c>
       <c r="M3" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N3" s="1">
-        <v>200</v>
+        <v>3000</v>
       </c>
       <c r="O3" s="1">
+        <v>100</v>
+      </c>
+      <c r="P3" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>1</v>
+      </c>
+      <c r="R3" s="1">
+        <v>1</v>
+      </c>
+      <c r="S3" s="1">
+        <v>3</v>
+      </c>
+      <c r="T3" s="1">
         <v>5</v>
       </c>
-      <c r="P3" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="1">
-        <v>0</v>
-      </c>
-      <c r="R3" s="1">
-        <v>2</v>
-      </c>
-      <c r="S3" s="1">
-        <v>1</v>
-      </c>
-      <c r="T3" s="1">
-        <v>1</v>
-      </c>
       <c r="U3" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
-        <v>20002</v>
+        <v>20001</v>
       </c>
       <c r="B4" s="1">
-        <v>20002</v>
+        <v>20001</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F4" s="1">
         <v>3</v>
@@ -813,7 +818,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="1">
-        <v>20002</v>
+        <v>20001</v>
       </c>
       <c r="I4" s="1">
         <v>2</v>
@@ -857,19 +862,19 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
-        <v>20003</v>
+        <v>20002</v>
       </c>
       <c r="B5" s="1">
-        <v>20003</v>
+        <v>20002</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>31</v>
+      <c r="D5" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F5" s="1">
         <v>3</v>
@@ -878,7 +883,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="1">
-        <v>20003</v>
+        <v>20002</v>
       </c>
       <c r="I5" s="1">
         <v>2</v>
@@ -896,7 +901,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O5" s="1">
         <v>5</v>
@@ -908,7 +913,7 @@
         <v>0</v>
       </c>
       <c r="R5" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S5" s="1">
         <v>1</v>
@@ -922,26 +927,28 @@
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
-        <v>30003</v>
+        <v>20003</v>
       </c>
       <c r="B6" s="1">
-        <v>30003</v>
+        <v>20003</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="5"/>
+        <v>27</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6" s="1">
-        <v>30003</v>
+        <v>20003</v>
       </c>
       <c r="I6" s="1">
         <v>2</v>
@@ -959,34 +966,91 @@
         <v>0</v>
       </c>
       <c r="N6" s="1">
+        <v>300</v>
+      </c>
+      <c r="O6" s="1">
+        <v>5</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1">
+        <v>3</v>
+      </c>
+      <c r="S6" s="1">
+        <v>1</v>
+      </c>
+      <c r="T6" s="1">
+        <v>1</v>
+      </c>
+      <c r="U6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A7" s="1">
+        <v>30003</v>
+      </c>
+      <c r="B7" s="1">
+        <v>30003</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>3</v>
+      </c>
+      <c r="H7" s="1">
+        <v>30003</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
         <v>1000</v>
       </c>
-      <c r="O6" s="1">
+      <c r="O7" s="1">
         <v>100</v>
       </c>
-      <c r="P6" s="1">
+      <c r="P7" s="1">
         <v>0.1</v>
       </c>
-      <c r="Q6" s="1">
-        <v>1</v>
-      </c>
-      <c r="R6" s="1">
-        <v>1</v>
-      </c>
-      <c r="S6" s="1">
-        <v>1</v>
-      </c>
-      <c r="T6" s="1">
+      <c r="Q7" s="1">
+        <v>1</v>
+      </c>
+      <c r="R7" s="1">
+        <v>1</v>
+      </c>
+      <c r="S7" s="1">
+        <v>1</v>
+      </c>
+      <c r="T7" s="1">
         <v>2</v>
       </c>
-      <c r="U6" s="1">
+      <c r="U7" s="1">
         <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="10:10" x14ac:dyDescent="0.45">
-      <c r="J35" s="1">
-        <f>35*300</f>
-        <v>10500</v>
       </c>
     </row>
   </sheetData>
